--- a/files/九龙-启德-天泷.xlsx
+++ b/files/九龙-启德-天泷.xlsx
@@ -27,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -128,18 +128,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="007F7F7F"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
@@ -225,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -290,16 +285,13 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -791,7 +783,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -866,7 +858,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -932,7 +924,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -1138,7 +1130,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1344,7 +1336,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1550,7 +1542,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1756,7 +1748,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1892,7 +1884,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1958,7 +1950,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -2094,7 +2086,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2160,7 +2152,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2296,7 +2288,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2362,7 +2354,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2428,7 +2420,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2494,7 +2486,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2560,7 +2552,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2626,7 +2618,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2692,7 +2684,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2758,7 +2750,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2894,7 +2886,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2960,7 +2952,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -3026,7 +3018,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3092,7 +3084,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3158,7 +3150,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3224,7 +3216,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3290,7 +3282,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3356,7 +3348,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3422,7 +3414,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3488,7 +3480,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3554,7 +3546,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3690,7 +3682,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3756,7 +3748,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3822,7 +3814,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3888,7 +3880,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3954,7 +3946,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -4020,7 +4012,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4086,7 +4078,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4152,7 +4144,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4358,7 +4350,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4424,7 +4416,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4490,7 +4482,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4556,7 +4548,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4622,7 +4614,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4688,7 +4680,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2023-05-28</t>
+          <t>2023-05-29</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4754,7 +4746,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4820,7 +4812,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4886,7 +4878,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4952,7 +4944,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -5018,7 +5010,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -5084,7 +5076,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -5150,7 +5142,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -5216,7 +5208,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5282,7 +5274,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5348,7 +5340,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5414,7 +5406,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5480,7 +5472,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5546,7 +5538,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5612,7 +5604,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5678,7 +5670,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5744,7 +5736,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5810,7 +5802,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5876,7 +5868,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5942,7 +5934,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -6008,7 +6000,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -6074,7 +6066,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -6140,7 +6132,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -6206,7 +6198,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -6692,7 +6684,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6828,7 +6820,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6964,7 +6956,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -7100,7 +7092,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -7236,7 +7228,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -7372,7 +7364,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -7438,7 +7430,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7504,7 +7496,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7640,7 +7632,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7706,7 +7698,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7772,7 +7764,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7838,7 +7830,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7904,7 +7896,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7970,7 +7962,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -8036,7 +8028,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -8102,7 +8094,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2023-05-30</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -8168,7 +8160,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -8234,7 +8226,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -8300,7 +8292,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -8366,7 +8358,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -8432,7 +8424,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8498,7 +8490,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8564,7 +8556,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8630,7 +8622,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8696,7 +8688,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8762,7 +8754,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8828,7 +8820,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8894,7 +8886,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8960,7 +8952,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -9026,7 +9018,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2023-11-30</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -9092,7 +9084,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -9158,7 +9150,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -9224,7 +9216,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -9290,7 +9282,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -9356,7 +9348,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -9422,7 +9414,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2023-06-01</t>
+          <t>2023-06-02</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -9488,7 +9480,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -9554,7 +9546,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9620,7 +9612,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9686,7 +9678,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9752,7 +9744,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9818,7 +9810,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9884,7 +9876,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9950,7 +9942,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -10156,7 +10148,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -11482,7 +11474,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -11548,7 +11540,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -11754,7 +11746,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -12030,7 +12022,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2025-01-14</t>
+          <t>2025-01-15</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -12306,7 +12298,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -12372,7 +12364,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -12578,7 +12570,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -12644,7 +12636,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -12850,7 +12842,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -12916,7 +12908,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -13122,7 +13114,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -13188,7 +13180,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -13394,7 +13386,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -13460,7 +13452,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -13666,7 +13658,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -13732,7 +13724,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -13938,7 +13930,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -14004,7 +13996,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -14210,7 +14202,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -14276,7 +14268,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -14482,7 +14474,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -14548,7 +14540,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -14754,7 +14746,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -14820,7 +14812,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -15026,7 +15018,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -15092,7 +15084,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -15298,7 +15290,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -15364,7 +15356,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -15570,7 +15562,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -15636,7 +15628,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -15842,7 +15834,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -15908,7 +15900,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -16114,7 +16106,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -16180,7 +16172,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -16386,7 +16378,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -16452,7 +16444,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -16658,7 +16650,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -16724,7 +16716,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -16930,7 +16922,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -16996,7 +16988,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2024-12-02</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -17202,7 +17194,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -17268,7 +17260,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -17474,7 +17466,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -17540,7 +17532,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2024-12-15</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -18166,7 +18158,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -18302,7 +18294,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -18438,7 +18430,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023-06-09</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -18504,7 +18496,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -18570,7 +18562,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -18636,7 +18628,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -18702,7 +18694,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -18838,7 +18830,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -18904,7 +18896,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -18970,7 +18962,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2024-12-10</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -19036,7 +19028,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -19102,7 +19094,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -19168,7 +19160,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -19234,7 +19226,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -19300,7 +19292,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -19366,7 +19358,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -19432,7 +19424,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -19498,7 +19490,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2024-11-25</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -19564,7 +19556,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -19630,7 +19622,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -19696,7 +19688,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -19762,7 +19754,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -19828,7 +19820,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -19894,7 +19886,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -19960,7 +19952,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -20026,7 +20018,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -20092,7 +20084,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -20158,7 +20150,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -20224,7 +20216,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -20290,7 +20282,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -20356,7 +20348,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -20422,7 +20414,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -20488,7 +20480,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -20554,7 +20546,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -20620,7 +20612,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -20686,7 +20678,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -20752,7 +20744,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -20818,7 +20810,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -20884,7 +20876,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -20950,7 +20942,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -21016,7 +21008,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -21082,7 +21074,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -21148,7 +21140,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -21214,7 +21206,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -21280,7 +21272,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -23096,7 +23088,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -23162,7 +23154,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -23438,7 +23430,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -23644,7 +23636,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -23710,7 +23702,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -23986,7 +23978,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -24192,7 +24184,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -24258,7 +24250,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -24464,7 +24456,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -24530,7 +24522,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -24736,7 +24728,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -24802,7 +24794,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -25008,7 +25000,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -25074,7 +25066,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -25280,7 +25272,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -25346,7 +25338,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -25832,7 +25824,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -25898,7 +25890,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -26104,7 +26096,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -26170,7 +26162,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -26376,7 +26368,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -26442,7 +26434,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -26648,7 +26640,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -26714,7 +26706,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -26920,7 +26912,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -26986,7 +26978,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -27192,7 +27184,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -27258,7 +27250,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -27464,7 +27456,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -27530,7 +27522,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -27736,7 +27728,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H401" s="5" t="n">
@@ -27802,7 +27794,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="H402" s="5" t="n">
@@ -28008,7 +28000,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -28074,7 +28066,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -28280,7 +28272,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="H409" s="5" t="n">
@@ -28346,7 +28338,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="H410" s="5" t="n">
@@ -28622,7 +28614,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H414" s="5" t="n">
@@ -28898,7 +28890,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="H418" s="5" t="n">
@@ -29594,7 +29586,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H428" s="5" t="n">
@@ -29660,7 +29652,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="H429" s="5" t="n">
@@ -29726,7 +29718,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="H430" s="5" t="n">
@@ -29792,7 +29784,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H431" s="5" t="n">
@@ -29858,7 +29850,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H432" s="5" t="n">
@@ -29924,7 +29916,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H433" s="5" t="n">
@@ -29990,7 +29982,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H434" s="5" t="n">
@@ -30056,7 +30048,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H435" s="5" t="n">
@@ -30122,7 +30114,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H436" s="5" t="n">
@@ -30188,7 +30180,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H437" s="5" t="n">
@@ -30254,7 +30246,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
@@ -30320,7 +30312,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H439" s="5" t="n">
@@ -30386,7 +30378,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H440" s="5" t="n">
@@ -30452,7 +30444,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H441" s="5" t="n">
@@ -30518,7 +30510,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="H442" s="5" t="n">
@@ -30584,7 +30576,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H443" s="5" t="n">
@@ -30650,7 +30642,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H444" s="5" t="n">
@@ -30716,7 +30708,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="H445" s="5" t="n">
@@ -30782,7 +30774,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H446" s="5" t="n">
@@ -30848,7 +30840,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="H447" s="5" t="n">
@@ -30914,7 +30906,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="H448" s="5" t="n">
@@ -30980,7 +30972,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H449" s="5" t="n">
@@ -31046,7 +31038,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H450" s="5" t="n">
@@ -31112,7 +31104,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H451" s="5" t="n">
@@ -31178,7 +31170,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="H452" s="5" t="n">
@@ -31244,7 +31236,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="H453" s="5" t="n">
@@ -31310,7 +31302,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="H454" s="5" t="n">
@@ -31376,7 +31368,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="H455" s="5" t="n">
@@ -31442,7 +31434,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="H456" s="5" t="n">
@@ -31508,7 +31500,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="H457" s="5" t="n">
@@ -31574,7 +31566,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="H458" s="5" t="n">
@@ -31640,7 +31632,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H459" s="5" t="n">
@@ -31706,7 +31698,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="H460" s="5" t="n">
@@ -31772,7 +31764,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="H461" s="5" t="n">
@@ -31838,7 +31830,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
@@ -31904,7 +31896,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H463" s="5" t="n">
@@ -31970,7 +31962,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H464" s="5" t="n">
@@ -32036,7 +32028,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H465" s="5" t="n">
@@ -32102,7 +32094,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H466" s="5" t="n">
@@ -32308,7 +32300,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-06-08</t>
         </is>
       </c>
       <c r="H469" s="5" t="n">
@@ -33634,7 +33626,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="H488" s="5" t="n">
@@ -33980,7 +33972,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H493" s="5" t="n">
@@ -34186,7 +34178,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="H496" s="5" t="n">
@@ -34532,7 +34524,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H501" s="5" t="n">
@@ -35018,7 +35010,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="H508" s="5" t="n">
@@ -35084,7 +35076,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="H509" s="5" t="n">
@@ -35290,7 +35282,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-30</t>
         </is>
       </c>
       <c r="H512" s="5" t="n">
@@ -35356,7 +35348,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="H513" s="5" t="n">
@@ -35562,7 +35554,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H516" s="5" t="n">
@@ -35628,7 +35620,7 @@
       </c>
       <c r="G517" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H517" s="5" t="n">
@@ -35834,7 +35826,7 @@
       </c>
       <c r="G520" s="3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="H520" s="5" t="n">
@@ -36110,7 +36102,7 @@
       </c>
       <c r="G524" s="3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="H524" s="5" t="n">
@@ -36386,7 +36378,7 @@
       </c>
       <c r="G528" s="3" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="H528" s="5" t="n">
@@ -36452,7 +36444,7 @@
       </c>
       <c r="G529" s="3" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="H529" s="5" t="n">
@@ -36938,7 +36930,7 @@
       </c>
       <c r="G536" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H536" s="5" t="n">
@@ -37004,7 +36996,7 @@
       </c>
       <c r="G537" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H537" s="5" t="n">
@@ -37210,7 +37202,7 @@
       </c>
       <c r="G540" s="3" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="H540" s="5" t="n">
@@ -37276,7 +37268,7 @@
       </c>
       <c r="G541" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H541" s="5" t="n">
@@ -37482,7 +37474,7 @@
       </c>
       <c r="G544" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H544" s="5" t="n">
@@ -37548,7 +37540,7 @@
       </c>
       <c r="G545" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H545" s="5" t="n">
@@ -37754,7 +37746,7 @@
       </c>
       <c r="G548" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H548" s="5" t="n">
@@ -37820,7 +37812,7 @@
       </c>
       <c r="G549" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H549" s="5" t="n">
@@ -38096,7 +38088,7 @@
       </c>
       <c r="G553" s="3" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="H553" s="5" t="n">
@@ -38722,7 +38714,7 @@
       </c>
       <c r="G562" s="3" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-06-28</t>
         </is>
       </c>
       <c r="H562" s="5" t="n">
@@ -38788,7 +38780,7 @@
       </c>
       <c r="G563" s="3" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>2024-04-03</t>
         </is>
       </c>
       <c r="H563" s="5" t="n">
@@ -38854,7 +38846,7 @@
       </c>
       <c r="G564" s="3" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="H564" s="5" t="n">
@@ -38920,7 +38912,7 @@
       </c>
       <c r="G565" s="3" t="inlineStr">
         <is>
-          <t>2023-07-31</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="H565" s="5" t="n">
@@ -38986,7 +38978,7 @@
       </c>
       <c r="G566" s="3" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="H566" s="5" t="n">
@@ -39052,7 +39044,7 @@
       </c>
       <c r="G567" s="3" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="H567" s="5" t="n">
@@ -39118,7 +39110,7 @@
       </c>
       <c r="G568" s="3" t="inlineStr">
         <is>
-          <t>2023-07-17</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="H568" s="5" t="n">
@@ -39224,12 +39216,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -39281,7 +39273,7 @@
           <t>A | 1942呎 (4+房)
 $11215万
 $57,750/呎
-(23年-06月-13日)</t>
+(23年-06月-14日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -39290,7 +39282,7 @@
           <t>C | 635呎 (3房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -39321,7 +39313,7 @@
           <t>C | 590呎 (3房)
 $1617万
 $27,399/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -39352,7 +39344,7 @@
           <t>C | 590呎 (3房)
 $1568万
 $26,576/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
     </row>
@@ -39383,7 +39375,7 @@
           <t>C | 590呎 (3房)
 $1588万
 $26,907/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -39393,7 +39385,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 1428呎 (4+房)
 招标单位
@@ -39401,7 +39393,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 1258呎 (4+房)
 招标单位
@@ -39414,7 +39406,7 @@
           <t>C | 590呎 (3房)
 $1540万
 $26,099/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -39429,7 +39421,7 @@
           <t>A | 1339呎 (4+房)
 $6740万
 $50,336/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -39445,7 +39437,7 @@
           <t>C | 590呎 (3房)
 $1575万
 $26,692/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -39460,10 +39452,10 @@
           <t>A | 1339呎 (4+房)
 $6665万
 $49,776/呎
-(26年-06月-16日)</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="inlineStr">
+(26年-06月-17日)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 1258呎 (4+房)
 招标单位
@@ -39476,7 +39468,7 @@
           <t>C | 590呎 (3房)
 $1568万
 $26,584/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -39491,10 +39483,10 @@
           <t>A | 1339呎 (4+房)
 $6007万
 $44,862/呎
-(25年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="C12" s="25" t="inlineStr">
+(25年-06月-04日)</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>B | 1258呎 (4+房)
 -
@@ -39507,7 +39499,7 @@
           <t>C | 590呎 (3房)
 $1562万
 $26,476/呎
-(26年-03月-18日)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
     </row>
@@ -39522,7 +39514,7 @@
           <t>A | 1339呎 (4+房)
 $6453万
 $48,193/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -39530,7 +39522,7 @@
           <t>B | 1171呎 (4+房)
 $5285万
 $45,132/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -39538,7 +39530,7 @@
           <t>C | 590呎 (3房)
 $1509万
 $25,577/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -39553,7 +39545,7 @@
           <t>A | 1428呎 (4+房)
 $5860万
 $41,036/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -39561,7 +39553,7 @@
           <t>B | 1171呎 (4+房)
 $4868万
 $41,571/呎
-(25年-10月-20日)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -39569,7 +39561,7 @@
           <t>C | 590呎 (3房)
 $1497万
 $25,369/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
     </row>
@@ -39584,10 +39576,10 @@
           <t>A | 1339呎 (4+房)
 $5810万
 $43,391/呎
-(25年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="C15" s="25" t="inlineStr">
+(25年-06月-04日)</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>B | 1258呎 (4+房)
 -
@@ -39600,7 +39592,7 @@
           <t>C | 590呎 (3房)
 $1537万
 $26,046/呎
-(26年-03月-10日)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
     </row>
@@ -39615,7 +39607,7 @@
           <t>A | 1339呎 (4+房)
 $6161万
 $46,012/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -39623,7 +39615,7 @@
           <t>B | 1171呎 (4+房)
 $4900万
 $41,845/呎
-(26年-02月-05日)</t>
+(26年-02月-06日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -39631,7 +39623,7 @@
           <t>C | 590呎 (3房)
 $1491万
 $25,264/呎
-(26年-03月-12日)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
     </row>
@@ -39646,7 +39638,7 @@
           <t>A | 1428呎 (4+房)
 $5733万
 $40,146/呎
-(25年-01月-05日)</t>
+(25年-01月-06日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -39654,7 +39646,7 @@
           <t>B | 1171呎 (4+房)
 $4756万
 $40,615/呎
-(25年-11月-26日)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -39662,7 +39654,7 @@
           <t>C | 590呎 (3房)
 $1524万
 $25,831/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
     </row>
@@ -39677,7 +39669,7 @@
           <t>A | 1339呎 (3房)
 $5832万
 $43,555/呎
-(25年-12月-30日)</t>
+(25年-12月-31日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -39685,7 +39677,7 @@
           <t>B | 1171呎 (4+房)
 $4719万
 $40,299/呎
-(25年-12月-30日)</t>
+(25年-12月-31日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -39693,7 +39685,7 @@
           <t>C | 590呎 (3房)
 $1465万
 $24,825/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -39708,10 +39700,10 @@
           <t>A | 1339呎 (4+房)
 $5976万
 $44,630/呎
-(26年-03月-29日)</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
+(26年-03月-30日)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 1258呎 (4+房)
 招标单位
@@ -39724,7 +39716,7 @@
           <t>C | 590呎 (3房)
 $1511万
 $25,615/呎
-(26年-03月-16日)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
     </row>
@@ -39739,7 +39731,7 @@
           <t>A | 1428呎 (4+房)
 $5633万
 $39,447/呎
-(25年-06月-03日)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -39747,7 +39739,7 @@
           <t>B | 1171呎 (4+房)
 $4568万
 $39,009/呎
-(25年-06月-08日)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -39755,7 +39747,7 @@
           <t>C | 590呎 (3房)
 $1486万
 $25,185/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
     </row>
@@ -39770,7 +39762,7 @@
           <t>A | 1339呎 (4+房)
 $5550万
 $41,449/呎
-(25年-05月-13日)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -39778,7 +39770,7 @@
           <t>B | 1171呎 (4+房)
 $4502万
 $38,446/呎
-(25年-05月-13日)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -39786,7 +39778,7 @@
           <t>C | 590呎 (3房)
 $1461万
 $24,763/呎
-(26年-03月-03日)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
     </row>
@@ -39817,7 +39809,7 @@
           <t>C | 590呎 (3房)
 $1405万
 $23,814/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
     </row>
@@ -39832,7 +39824,7 @@
           <t>A | 1339呎 (4+房)
 $5657万
 $42,248/呎
-(25年-08月-18日)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -39840,7 +39832,7 @@
           <t>B | 1171呎 (4+房)
 $4790万
 $40,905/呎
-(26年-07月-19日)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -39848,7 +39840,7 @@
           <t>C | 590呎 (3房)
 $1440万
 $24,410/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
     </row>
@@ -39863,7 +39855,7 @@
           <t>A | 1428呎 (4+房)
 $5614万
 $39,314/呎
-(23年-05月-28日)</t>
+(23年-05月-29日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -39871,7 +39863,7 @@
           <t>B | 1171呎 (4+房)
 $4763万
 $40,675/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -39879,7 +39871,7 @@
           <t>C | 590呎 (3房)
 $1422万
 $24,108/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
     </row>
@@ -39894,7 +39886,7 @@
           <t>A | 1339呎 (4+房)
 $5468万
 $40,833/呎
-(24年-12月-02日)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -39902,7 +39894,7 @@
           <t>B | 1171呎 (4+房)
 $4711万
 $40,231/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -39910,7 +39902,7 @@
           <t>C | 590呎 (3房)
 $1416万
 $24,001/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
     </row>
@@ -39925,7 +39917,7 @@
           <t>A | 1339呎 (4+房)
 $5558万
 $41,509/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -39933,7 +39925,7 @@
           <t>B | 1171呎 (4+房)
 $4510万
 $38,514/呎
-(25年-11月-02日)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -39941,7 +39933,7 @@
           <t>C | 590呎 (3房)
 $1410万
 $23,893/呎
-(26年-03月-08日)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
     </row>
@@ -39956,7 +39948,7 @@
           <t>A | 1339呎 (4+房)
 $5546万
 $41,419/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -39964,7 +39956,7 @@
           <t>B | 1171呎 (4+房)
 $4493万
 $38,369/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -39972,7 +39964,7 @@
           <t>C | 590呎 (3房)
 $1407万
 $23,839/呎
-(26年-03月-04日)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
     </row>
@@ -39987,7 +39979,7 @@
           <t>A | 1339呎 (4+房)
 $5365万
 $40,067/呎
-(25年-06月-11日)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -39995,7 +39987,7 @@
           <t>B | 1171呎 (4+房)
 $4557万
 $38,915/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -40003,7 +39995,7 @@
           <t>C | 590呎 (3房)
 $1361万
 $23,072/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -40018,7 +40010,7 @@
           <t>A | 1339呎 (4+房)
 $5432万
 $40,568/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -40026,7 +40018,7 @@
           <t>B | 1171呎 (4+房)
 $4408万
 $37,643/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -40034,7 +40026,7 @@
           <t>C | 590呎 (3房)
 $1397万
 $23,678/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
     </row>
@@ -40049,7 +40041,7 @@
           <t>A | 1339呎 (4+房)
 $5393万
 $40,275/呎
-(25年-07月-29日)</t>
+(25年-07月-30日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -40057,7 +40049,7 @@
           <t>B | 1171呎 (4+房)
 $4379万
 $37,395/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -40065,7 +40057,7 @@
           <t>C | 590呎 (3房)
 $1349万
 $22,864/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -40080,7 +40072,7 @@
           <t>A | 1339呎 (4+房)
 $5327万
 $39,783/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -40088,7 +40080,7 @@
           <t>B | 1171呎 (4+房)
 $4460万
 $38,087/呎
-(26年-02月-03日)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -40096,7 +40088,7 @@
           <t>C | 590呎 (3房)
 $1324万
 $22,446/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
     </row>
@@ -40111,7 +40103,7 @@
           <t>A | 1339呎 (4+房)
 $5223万
 $39,007/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -40119,7 +40111,7 @@
           <t>B | 1171呎 (4+房)
 $4412万
 $37,677/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr"/>
@@ -40272,7 +40264,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 1002呎 (3房)
 招标单位
@@ -40295,7 +40287,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 920呎 (3房)
 招标单位
@@ -40310,7 +40302,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 1173呎 (4+房)
 招标单位
@@ -40323,7 +40315,7 @@
           <t>B | 920呎 (3房)
 $3982万
 $43,283/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -40333,7 +40325,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 1173呎 (4+房)
 招标单位
@@ -40346,7 +40338,7 @@
           <t>B | 920呎 (3房)
 $3889万
 $42,272/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
     </row>
@@ -40369,7 +40361,7 @@
           <t>B | 920呎 (3房)
 $3638万
 $39,543/呎
-(25年-11月-18日)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
     </row>
@@ -40379,7 +40371,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 1173呎 (4+房)
 招标单位
@@ -40392,7 +40384,7 @@
           <t>B | 920呎 (3房)
 $3610万
 $39,239/呎
-(25年-12月-21日)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
     </row>
@@ -40402,7 +40394,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 1173呎 (4+房)
 招标单位
@@ -40415,7 +40407,7 @@
           <t>B | 920呎 (3房)
 $3454万
 $37,543/呎
-(25年-03月-24日)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
     </row>
@@ -40430,7 +40422,7 @@
           <t>A | 1076呎 (4+房)
 $4590万
 $42,658/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -40438,7 +40430,7 @@
           <t>B | 1002呎 (3房)
 $3390万
 $33,832/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -40448,7 +40440,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 1173呎 (4+房)
 招标单位
@@ -40461,7 +40453,7 @@
           <t>B | 1002呎 (3房)
 $3345万
 $33,383/呎
-(24年-06月-25日)</t>
+(24年-06月-26日)</t>
         </is>
       </c>
     </row>
@@ -40476,7 +40468,7 @@
           <t>A | 1173呎 (4+房)
 $4111万
 $35,047/呎
-(25年-06月-03日)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -40484,7 +40476,7 @@
           <t>B | 1002呎 (3房)
 $3310万
 $33,034/呎
-(24年-05月-01日)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
     </row>
@@ -40499,7 +40491,7 @@
           <t>A | 1076呎 (4+房)
 $4388万
 $40,781/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -40507,7 +40499,7 @@
           <t>B | 920呎 (3房)
 $3306万
 $35,935/呎
-(24年-06月-03日)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
     </row>
@@ -40522,7 +40514,7 @@
           <t>A | 1076呎 (4+房)
 $4365万
 $40,567/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -40530,7 +40522,7 @@
           <t>B | 1002呎 (3房)
 $3286万
 $32,794/呎
-(24年-05月-09日)</t>
+(24年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -40545,7 +40537,7 @@
           <t>A | 1173呎 (4+房)
 $4100万
 $34,953/呎
-(23年-05月-30日)</t>
+(23年-05月-31日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -40553,7 +40545,7 @@
           <t>B | 1002呎 (3房)
 $3270万
 $32,635/呎
-(24年-07月-14日)</t>
+(24年-07月-15日)</t>
         </is>
       </c>
     </row>
@@ -40568,7 +40560,7 @@
           <t>A | 1076呎 (4+房)
 $4038万
 $37,528/呎
-(25年-07月-03日)</t>
+(25年-07月-04日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -40576,7 +40568,7 @@
           <t>B | 920呎 (3房)
 $3303万
 $35,902/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
     </row>
@@ -40591,7 +40583,7 @@
           <t>A | 1173呎 (4+房)
 $3990万
 $34,015/呎
-(24年-04月-22日)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -40599,7 +40591,7 @@
           <t>B | 1002呎 (3房)
 $3228万
 $32,216/呎
-(24年-04月-22日)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -40614,7 +40606,7 @@
           <t>A | 1173呎 (4+房)
 $3965万
 $33,802/呎
-(24年-03月-27日)</t>
+(24年-03月-28日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -40622,7 +40614,7 @@
           <t>B | 1002呎 (3房)
 $3190万
 $31,836/呎
-(24年-04月-04日)</t>
+(24年-04月-05日)</t>
         </is>
       </c>
     </row>
@@ -40637,7 +40629,7 @@
           <t>A | 1173呎 (4+房)
 $3921万
 $33,427/呎
-(23年-11月-09日)</t>
+(23年-11月-10日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -40645,7 +40637,7 @@
           <t>B | 1002呎 (3房)
 $3157万
 $31,507/呎
-(23年-05月-18日)</t>
+(23年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -40660,7 +40652,7 @@
           <t>A | 1173呎 (4+房)
 $3997万
 $34,075/呎
-(24年-10月-31日)</t>
+(24年-11月-01日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -40668,7 +40660,7 @@
           <t>B | 920呎 (3房)
 $3140万
 $34,130/呎
-(24年-03月-24日)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
     </row>
@@ -40683,7 +40675,7 @@
           <t>A | 1173呎 (4+房)
 $3972万
 $33,862/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -40691,7 +40683,7 @@
           <t>B | 920呎 (3房)
 $3219万
 $34,989/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
     </row>
@@ -40706,7 +40698,7 @@
           <t>A | 1173呎 (4+房)
 $3861万
 $32,917/呎
-(23年-11月-29日)</t>
+(23年-11月-30日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -40714,7 +40706,7 @@
           <t>B | 1002呎 (3房)
 $3130万
 $31,238/呎
-(24年-05月-09日)</t>
+(24年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -40729,7 +40721,7 @@
           <t>A | 1173呎 (4+房)
 $3910万
 $33,333/呎
-(23年-07月-19日)</t>
+(23年-07月-20日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -40737,7 +40729,7 @@
           <t>B | 1002呎 (3房)
 $3093万
 $30,868/呎
-(24年-04月-18日)</t>
+(24年-04月-19日)</t>
         </is>
       </c>
     </row>
@@ -40752,7 +40744,7 @@
           <t>A | 1076呎 (4+房)
 $3836万
 $35,651/呎
-(24年-04月-18日)</t>
+(24年-04月-19日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -40760,7 +40752,7 @@
           <t>B | 1002呎 (3房)
 $3103万
 $30,968/呎
-(24年-05月-02日)</t>
+(24年-05月-03日)</t>
         </is>
       </c>
     </row>
@@ -40775,7 +40767,7 @@
           <t>A | 1173呎 (4+房)
 $3854万
 $32,856/呎
-(23年-06月-01日)</t>
+(23年-06月-02日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -40783,7 +40775,7 @@
           <t>B | 920呎 (3房)
 $3138万
 $34,109/呎
-(25年-09月-03日)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
     </row>
@@ -40798,7 +40790,7 @@
           <t>A | 1173呎 (4+房)
 $3780万
 $32,225/呎
-(24年-05月-06日)</t>
+(24年-05月-07日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -40806,7 +40798,7 @@
           <t>B | 920呎 (3房)
 $3044万
 $33,087/呎
-(24年-05月-06日)</t>
+(24年-05月-07日)</t>
         </is>
       </c>
     </row>
@@ -40821,7 +40813,7 @@
           <t>A | 1076呎 (4+房)
 $3730万
 $34,667/呎
-(24年-06月-05日)</t>
+(24年-06月-06日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -40829,7 +40821,7 @@
           <t>B | 920呎 (3房)
 $3032万
 $32,957/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -40844,7 +40836,7 @@
           <t>A | 1076呎 (4+房)
 $3715万
 $34,526/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -40852,7 +40844,7 @@
           <t>B | 920呎 (3房)
 $3028万
 $32,913/呎
-(25年-04月-01日)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -40867,7 +40859,7 @@
           <t>A | 1076呎 (4+房)
 $3651万
 $33,931/呎
-(25年-05月-20日)</t>
+(25年-05月-21日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -40875,7 +40867,7 @@
           <t>B | 1002呎 (3房)
 $2960万
 $29,541/呎
-(25年-03月-31日)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -41013,7 +41005,7 @@
           <t>A | 1677呎 (4+房)
 $9203万
 $54,880/呎
-(23年-06月-27日)</t>
+(23年-06月-28日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -41157,7 +41149,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 1102呎 (3房)
 招标单位
@@ -41165,7 +41157,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 1085呎 (3房)
 招标单位
@@ -41201,7 +41193,7 @@
           <t>A | 1102呎 (3房)
 $4042万
 $36,679/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -41209,7 +41201,7 @@
           <t>B | 1085呎 (3房)
 $4002万
 $36,885/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -41235,7 +41227,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 1102呎 (3房)
 招标单位
@@ -41248,7 +41240,7 @@
           <t>B | 994呎 (3房)
 $4060万
 $40,845/呎
-(25年-12月-16日)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -41274,7 +41266,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 1102呎 (3房)
 招标单位
@@ -41287,7 +41279,7 @@
           <t>B | 994呎 (3房)
 $3860万
 $38,833/呎
-(25年-01月-14日)</t>
+(25年-01月-15日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -41318,7 +41310,7 @@
           <t>A | 1102呎 (3房)
 $3774万
 $34,247/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -41326,7 +41318,7 @@
           <t>B | 1085呎 (3房)
 $3774万
 $34,783/呎
-(24年-12月-02日)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -41357,7 +41349,7 @@
           <t>A | 1102呎 (3房)
 $3708万
 $33,648/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -41365,7 +41357,7 @@
           <t>B | 994呎 (3房)
 $3752万
 $37,746/呎
-(25年-01月-09日)</t>
+(25年-01月-10日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -41396,7 +41388,7 @@
           <t>A | 1027呎 (3房)
 $3680万
 $35,833/呎
-(24年-04月-28日)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -41404,7 +41396,7 @@
           <t>B | 994呎 (3房)
 $3660万
 $36,821/呎
-(24年-04月-28日)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -41435,7 +41427,7 @@
           <t>A | 1102呎 (3房)
 $3671万
 $33,312/呎
-(24年-12月-02日)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -41443,7 +41435,7 @@
           <t>B | 1085呎 (3房)
 $3672万
 $33,843/呎
-(24年-12月-02日)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -41474,7 +41466,7 @@
           <t>A | 1027呎 (3房)
 $4114万
 $40,057/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -41482,7 +41474,7 @@
           <t>B | 994呎 (3房)
 $4960万
 $49,899/呎
-(26年-06月-23日)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -41513,7 +41505,7 @@
           <t>A | 1102呎 (3房)
 $3700万
 $33,575/呎
-(24年-04月-04日)</t>
+(24年-04月-05日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -41521,7 +41513,7 @@
           <t>B | 994呎 (3房)
 $3629万
 $36,509/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -41552,7 +41544,7 @@
           <t>A | 1102呎 (3房)
 $3627万
 $32,913/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -41560,7 +41552,7 @@
           <t>B | 1085呎 (3房)
 $3627万
 $33,428/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -41591,7 +41583,7 @@
           <t>A | 1027呎 (3房)
 $3584万
 $34,898/呎
-(24年-12月-02日)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -41599,7 +41591,7 @@
           <t>B | 1085呎 (3房)
 $3584万
 $33,032/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -41630,7 +41622,7 @@
           <t>A | 1027呎 (3房)
 $3563万
 $34,693/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -41638,7 +41630,7 @@
           <t>B | 1085呎 (3房)
 $3562万
 $32,832/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -41669,7 +41661,7 @@
           <t>A | 1027呎 (3房)
 $3593万
 $34,985/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -41677,7 +41669,7 @@
           <t>B | 994呎 (3房)
 $3540万
 $35,611/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -41708,7 +41700,7 @@
           <t>A | 1102呎 (3房)
 $3520万
 $31,942/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -41716,7 +41708,7 @@
           <t>B | 1085呎 (3房)
 $3518万
 $32,426/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -41747,7 +41739,7 @@
           <t>A | 1102呎 (3房)
 $3497万
 $31,730/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -41755,7 +41747,7 @@
           <t>B | 1085呎 (3房)
 $3497万
 $32,228/呎
-(24年-11月-17日)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -41786,7 +41778,7 @@
           <t>A | 1027呎 (3房)
 $3880万
 $37,780/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -41794,7 +41786,7 @@
           <t>B | 994呎 (3房)
 $3555万
 $35,765/呎
-(24年-12月-03日)</t>
+(24年-12月-04日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -41825,7 +41817,7 @@
           <t>A | 1102呎 (3房)
 $3454万
 $31,338/呎
-(24年-12月-02日)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -41833,7 +41825,7 @@
           <t>B | 994呎 (3房)
 $3454万
 $34,744/呎
-(24年-11月-17日)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -41864,7 +41856,7 @@
           <t>A | 1102呎 (3房)
 $3464万
 $31,434/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -41872,7 +41864,7 @@
           <t>B | 1085呎 (3房)
 $3524万
 $32,479/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -41903,7 +41895,7 @@
           <t>A | 1102呎 (3房)
 $3428万
 $31,107/呎
-(24年-12月-15日)</t>
+(24年-12月-16日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -41911,7 +41903,7 @@
           <t>B | 1085呎 (3房)
 $3450万
 $31,797/呎
-(24年-12月-15日)</t>
+(24年-12月-16日)</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -41942,7 +41934,7 @@
           <t>A | 1102呎 (3房)
 $3388万
 $30,744/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -41950,7 +41942,7 @@
           <t>B | 1085呎 (3房)
 $3388万
 $31,226/呎
-(24年-11月-21日)</t>
+(24年-11月-22日)</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
@@ -41981,7 +41973,7 @@
           <t>A | 1102呎 (3房)
 $3357万
 $30,463/呎
-(24年-12月-02日)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -41989,7 +41981,7 @@
           <t>B | 994呎 (3房)
 $3351万
 $33,712/呎
-(24年-12月-05日)</t>
+(24年-12月-06日)</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -42020,7 +42012,7 @@
           <t>A | 1027呎 (3房)
 $3323万
 $32,356/呎
-(25年-04月-07日)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -42028,7 +42020,7 @@
           <t>B | 1085呎 (3房)
 $3290万
 $30,323/呎
-(25年-02月-27日)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
@@ -42059,7 +42051,7 @@
           <t>A | 1102呎 (3房)
 $3258万
 $29,564/呎
-(24年-12月-15日)</t>
+(24年-12月-16日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -42067,7 +42059,7 @@
           <t>B | 994呎 (3房)
 $3530万
 $35,513/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
@@ -42273,7 +42265,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 1382呎 (4+房)
 招标单位
@@ -42281,7 +42273,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 1382呎 (4+房)
 招标单位
@@ -42296,7 +42288,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 1382呎 (4+房)
 招标单位
@@ -42309,7 +42301,7 @@
           <t>B | 1282呎 (4+房)
 $6036万
 $47,083/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -42319,7 +42311,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 1382呎 (4+房)
 招标单位
@@ -42332,7 +42324,7 @@
           <t>B | 1282呎 (4+房)
 $5982万
 $46,661/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -42347,7 +42339,7 @@
           <t>A | 1282呎 (4+房)
 $5591万
 $43,612/呎
-(25年-11月-26日)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -42355,7 +42347,7 @@
           <t>B | 1382呎 (4+房)
 $5390万
 $39,001/呎
-(23年-06月-08日)</t>
+(23年-06月-09日)</t>
         </is>
       </c>
     </row>
@@ -42370,7 +42362,7 @@
           <t>A | 1382呎 (4+房)
 $5373万
 $38,878/呎
-(25年-02月-19日)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -42378,7 +42370,7 @@
           <t>B | 1382呎 (4+房)
 $5373万
 $38,878/呎
-(25年-02月-19日)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
     </row>
@@ -42388,7 +42380,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>A | 1382呎 (4+房)
 -
@@ -42401,7 +42393,7 @@
           <t>B | 1282呎 (4+房)
 $5432万
 $42,371/呎
-(25年-09月-09日)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
     </row>
@@ -42416,7 +42408,7 @@
           <t>A | 1382呎 (4+房)
 $5380万
 $38,929/呎
-(23年-06月-07日)</t>
+(23年-06月-08日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -42424,7 +42416,7 @@
           <t>B | 1382呎 (4+房)
 $5380万
 $38,929/呎
-(23年-06月-07日)</t>
+(23年-06月-08日)</t>
         </is>
       </c>
     </row>
@@ -42439,7 +42431,7 @@
           <t>A | 1382呎 (4+房)
 $5227万
 $37,822/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -42447,7 +42439,7 @@
           <t>B | 1282呎 (4+房)
 $5226万
 $40,767/呎
-(24年-12月-10日)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
     </row>
@@ -42462,7 +42454,7 @@
           <t>A | 1282呎 (4+房)
 $5195万
 $40,523/呎
-(25年-05月-05日)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -42470,7 +42462,7 @@
           <t>B | 1282呎 (4+房)
 $5195万
 $40,523/呎
-(25年-06月-05日)</t>
+(25年-06月-06日)</t>
         </is>
       </c>
     </row>
@@ -42485,7 +42477,7 @@
           <t>A | 1382呎 (4+房)
 $5165万
 $37,370/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -42493,7 +42485,7 @@
           <t>B | 1382呎 (4+房)
 $5145万
 $37,229/呎
-(24年-04月-08日)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
     </row>
@@ -42508,7 +42500,7 @@
           <t>A | 1282呎 (4+房)
 $5246万
 $40,919/呎
-(25年-11月-04日)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -42516,7 +42508,7 @@
           <t>B | 1382呎 (4+房)
 $5134万
 $37,151/呎
-(24年-11月-20日)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
     </row>
@@ -42531,7 +42523,7 @@
           <t>A | 1282呎 (4+房)
 $5428万
 $42,340/呎
-(26年-02月-23日)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -42539,7 +42531,7 @@
           <t>B | 1382呎 (4+房)
 $5134万
 $37,149/呎
-(24年-11月-25日)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -42554,7 +42546,7 @@
           <t>A | 1382呎 (4+房)
 $5080万
 $36,758/呎
-(25年-06月-03日)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -42562,7 +42554,7 @@
           <t>B | 1382呎 (4+房)
 $5080万
 $36,758/呎
-(25年-06月-03日)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
     </row>
@@ -42577,7 +42569,7 @@
           <t>A | 1382呎 (4+房)
 $5043万
 $36,491/呎
-(24年-04月-23日)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -42585,7 +42577,7 @@
           <t>B | 1382呎 (4+房)
 $5042万
 $36,484/呎
-(24年-11月-04日)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -42600,7 +42592,7 @@
           <t>A | 1282呎 (4+房)
 $5070万
 $39,548/呎
-(25年-08月-19日)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -42608,7 +42600,7 @@
           <t>B | 1282呎 (4+房)
 $5070万
 $39,548/呎
-(25年-08月-31日)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
     </row>
@@ -42623,7 +42615,7 @@
           <t>A | 1282呎 (4+房)
 $4981万
 $38,853/呎
-(25年-04月-23日)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -42631,7 +42623,7 @@
           <t>B | 1282呎 (4+房)
 $5060万
 $39,470/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
     </row>
@@ -42646,7 +42638,7 @@
           <t>A | 1282呎 (4+房)
 $5050万
 $39,392/呎
-(25年-11月-24日)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -42654,7 +42646,7 @@
           <t>B | 1282呎 (4+房)
 $5050万
 $39,392/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
     </row>
@@ -42669,7 +42661,7 @@
           <t>A | 1282呎 (4+房)
 $4898万
 $38,206/呎
-(25年-05月-07日)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -42677,7 +42669,7 @@
           <t>B | 1282呎 (4+房)
 $4898万
 $38,206/呎
-(25年-05月-07日)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
     </row>
@@ -42692,7 +42684,7 @@
           <t>A | 1282呎 (4+房)
 $4995万
 $38,963/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -42700,7 +42692,7 @@
           <t>B | 1382呎 (4+房)
 $4888万
 $35,371/呎
-(24年-11月-27日)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
     </row>
@@ -42715,7 +42707,7 @@
           <t>A | 1282呎 (4+房)
 $4966万
 $38,736/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -42723,7 +42715,7 @@
           <t>B | 1282呎 (4+房)
 $4966万
 $38,736/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
     </row>
@@ -42738,7 +42730,7 @@
           <t>A | 1282呎 (4+房)
 $4908万
 $38,284/呎
-(25年-10月-29日)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -42746,7 +42738,7 @@
           <t>B | 1282呎 (4+房)
 $4908万
 $38,284/呎
-(25年-10月-29日)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
     </row>
@@ -42761,7 +42753,7 @@
           <t>A | 1282呎 (4+房)
 $4814万
 $37,549/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -42769,7 +42761,7 @@
           <t>B | 1282呎 (4+房)
 $4819万
 $37,590/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
     </row>
@@ -42784,7 +42776,7 @@
           <t>A | 1282呎 (4+房)
 $4845万
 $37,793/呎
-(25年-11月-24日)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -42792,7 +42784,7 @@
           <t>B | 1282呎 (4+房)
 $4961万
 $38,697/呎
-(25年-12月-23日)</t>
+(25年-12月-24日)</t>
         </is>
       </c>
     </row>
@@ -42807,7 +42799,7 @@
           <t>A | 1282呎 (4+房)
 $4882万
 $38,081/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -42815,7 +42807,7 @@
           <t>B | 1282呎 (4+房)
 $4753万
 $37,075/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
     </row>
@@ -42830,7 +42822,7 @@
           <t>A | 1282呎 (4+房)
 $4868万
 $37,972/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -42838,7 +42830,7 @@
           <t>B | 1282呎 (4+房)
 $4877万
 $38,042/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
     </row>
@@ -42971,7 +42963,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>A | 1677呎 (4+房)
 -
@@ -43120,7 +43112,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 1085呎 (3房)
 招标单位
@@ -43128,7 +43120,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 1102呎 (3房)
 招标单位
@@ -43159,7 +43151,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 1085呎 (3房)
 招标单位
@@ -43167,7 +43159,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 1102呎 (3房)
 招标单位
@@ -43203,7 +43195,7 @@
           <t>A | 992呎 (3房)
 $4469万
 $45,050/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -43211,7 +43203,7 @@
           <t>B | 1027呎 (3房)
 $4518万
 $43,992/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -43242,7 +43234,7 @@
           <t>A | 992呎 (3房)
 $4405万
 $44,405/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -43281,7 +43273,7 @@
           <t>A | 992呎 (3房)
 $4341万
 $43,760/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -43289,7 +43281,7 @@
           <t>B | 1027呎 (3房)
 $4427万
 $43,106/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -43320,10 +43312,10 @@
           <t>A | 992呎 (3房)
 $4217万
 $42,510/呎
-(26年-02月-24日)</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
+(26年-02月-25日)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 1102呎 (3房)
 招标单位
@@ -43359,7 +43351,7 @@
           <t>A | 992呎 (3房)
 $3865万
 $38,962/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -43367,7 +43359,7 @@
           <t>B | 1027呎 (3房)
 $4300万
 $41,870/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -43398,7 +43390,7 @@
           <t>A | 992呎 (3房)
 $3843万
 $38,740/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -43406,7 +43398,7 @@
           <t>B | 1027呎 (3房)
 $3885万
 $37,829/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -43437,7 +43429,7 @@
           <t>A | 992呎 (3房)
 $3898万
 $39,294/呎
-(25年-11月-24日)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -43445,7 +43437,7 @@
           <t>B | 1027呎 (3房)
 $4129万
 $40,204/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -43476,7 +43468,7 @@
           <t>A | 992呎 (3房)
 $3820万
 $38,508/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -43484,7 +43476,7 @@
           <t>B | 1027呎 (3房)
 $3935万
 $38,315/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -43515,7 +43507,7 @@
           <t>A | 992呎 (3房)
 $3818万
 $38,488/呎
-(25年-11月-09日)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -43523,7 +43515,7 @@
           <t>B | 1027呎 (3房)
 $3878万
 $37,760/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -43549,7 +43541,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>A | 1085呎 (3房)
 -
@@ -43593,7 +43585,7 @@
           <t>A | 992呎 (3房)
 $3740万
 $37,702/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -43601,7 +43593,7 @@
           <t>B | 1027呎 (3房)
 $3780万
 $36,806/呎
-(25年-09月-09日)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -43632,7 +43624,7 @@
           <t>A | 992呎 (3房)
 $3730万
 $37,601/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -43640,7 +43632,7 @@
           <t>B | 1027呎 (3房)
 $3700万
 $36,027/呎
-(25年-07月-13日)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -43671,7 +43663,7 @@
           <t>A | 992呎 (3房)
 $3679万
 $37,087/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -43679,7 +43671,7 @@
           <t>B | 1027呎 (3房)
 $3728万
 $36,300/呎
-(25年-07月-13日)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -43710,7 +43702,7 @@
           <t>A | 992呎 (3房)
 $3600万
 $36,290/呎
-(25年-06月-12日)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -43718,7 +43710,7 @@
           <t>B | 1027呎 (3房)
 $3640万
 $35,443/呎
-(25年-05月-05日)</t>
+(25年-05月-06日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -43749,7 +43741,7 @@
           <t>A | 1085呎 (3房)
 $3587万
 $33,060/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -43757,7 +43749,7 @@
           <t>B | 1102呎 (3房)
 $3618万
 $32,831/呎
-(25年-07月-06日)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -43788,7 +43780,7 @@
           <t>A | 992呎 (3房)
 $3565万
 $35,938/呎
-(25年-04月-24日)</t>
+(25年-04月-25日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -43796,7 +43788,7 @@
           <t>B | 1102呎 (3房)
 $3603万
 $32,695/呎
-(25年-05月-20日)</t>
+(25年-05月-21日)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -43827,7 +43819,7 @@
           <t>A | 992呎 (3房)
 $3626万
 $36,552/呎
-(25年-08月-19日)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -43835,7 +43827,7 @@
           <t>B | 1027呎 (3房)
 $3664万
 $35,677/呎
-(25年-08月-19日)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -43866,7 +43858,7 @@
           <t>A | 992呎 (3房)
 $3453万
 $34,808/呎
-(25年-05月-26日)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -43874,7 +43866,7 @@
           <t>B | 1027呎 (3房)
 $3653万
 $35,570/呎
-(25年-09月-01日)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -43905,7 +43897,7 @@
           <t>A | 992呎 (3房)
 $3274万
 $33,004/呎
-(25年-04月-07日)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -43913,7 +43905,7 @@
           <t>B | 1042呎 (3房)
 $3771万
 $36,190/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
@@ -43944,7 +43936,7 @@
           <t>A | 1085呎 (3房)
 $3230万
 $29,770/呎
-(25年-04月-16日)</t>
+(25年-04月-17日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -43952,7 +43944,7 @@
           <t>B | 1042呎 (3房)
 $3193万
 $30,643/呎
-(25年-04月-16日)</t>
+(25年-04月-17日)</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -43983,10 +43975,10 @@
           <t>A | 992呎 (3房)
 $3184万
 $32,097/呎
-(25年-04月-07日)</t>
-        </is>
-      </c>
-      <c r="C31" s="24" t="inlineStr">
+(25年-04月-08日)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>B | 1117呎 (3房)
 招标单位
@@ -44022,10 +44014,10 @@
           <t>A | 1085呎 (3房)
 $3127万
 $28,820/呎
-(25年-05月-13日)</t>
-        </is>
-      </c>
-      <c r="C32" s="24" t="inlineStr">
+(25年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>B | 1117呎 (3房)
 招标单位
@@ -44236,7 +44228,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 1002呎 (3房)
 招标单位
@@ -44244,7 +44236,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 1173呎 (4+房)
 招标单位
@@ -44264,10 +44256,10 @@
           <t>A | 920呎 (3房)
 $4111万
 $44,685/呎
-(26年-05月-31日)</t>
-        </is>
-      </c>
-      <c r="C9" s="24" t="inlineStr">
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 1173呎 (4+房)
 招标单位
@@ -44287,7 +44279,7 @@
           <t>A | 920呎 (3房)
 $3835万
 $41,685/呎
-(26年-01月-22日)</t>
+(26年-01月-23日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -44295,7 +44287,7 @@
           <t>B | 1076呎 (4+房)
 $4636万
 $43,086/呎
-(26年-01月-22日)</t>
+(26年-01月-23日)</t>
         </is>
       </c>
     </row>
@@ -44310,7 +44302,7 @@
           <t>A | 920呎 (3房)
 $3675万
 $39,946/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -44318,7 +44310,7 @@
           <t>B | 1076呎 (4+房)
 $4430万
 $41,171/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
     </row>
@@ -44333,7 +44325,7 @@
           <t>A | 920呎 (3房)
 $3643万
 $39,598/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -44341,7 +44333,7 @@
           <t>B | 1076呎 (4+房)
 $4405万
 $40,939/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
     </row>
@@ -44356,7 +44348,7 @@
           <t>A | 1002呎 (3房)
 $3613万
 $36,058/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -44364,7 +44356,7 @@
           <t>B | 1173呎 (4+房)
 $4370万
 $37,255/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
     </row>
@@ -44379,7 +44371,7 @@
           <t>A | 920呎 (3房)
 $3580万
 $38,913/呎
-(25年-08月-05日)</t>
+(25年-08月-06日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -44387,7 +44379,7 @@
           <t>B | 1076呎 (4+房)
 $4345万
 $40,381/呎
-(25年-08月-17日)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
     </row>
@@ -44402,7 +44394,7 @@
           <t>A | 920呎 (3房)
 $3534万
 $38,413/呎
-(25年-07月-23日)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -44410,7 +44402,7 @@
           <t>B | 1076呎 (4+房)
 $4298万
 $39,944/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
     </row>
@@ -44425,7 +44417,7 @@
           <t>A | 920呎 (3房)
 $3472万
 $37,739/呎
-(25年-06月-09日)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -44433,7 +44425,7 @@
           <t>B | 1173呎 (4+房)
 $4214万
 $35,925/呎
-(25年-07月-08日)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
     </row>
@@ -44448,7 +44440,7 @@
           <t>A | 920呎 (3房)
 $3513万
 $38,185/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -44456,7 +44448,7 @@
           <t>B | 1076呎 (4+房)
 $4246万
 $39,461/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
     </row>
@@ -44471,7 +44463,7 @@
           <t>A | 920呎 (3房)
 $3498万
 $38,022/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -44479,7 +44471,7 @@
           <t>B | 1076呎 (4+房)
 $4228万
 $39,294/呎
-(25年-07月-24日)</t>
+(25年-07月-25日)</t>
         </is>
       </c>
     </row>
@@ -44494,7 +44486,7 @@
           <t>A | 920呎 (3房)
 $3421万
 $37,185/呎
-(25年-04月-14日)</t>
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -44502,7 +44494,7 @@
           <t>B | 1173呎 (4+房)
 $4140万
 $35,294/呎
-(25年-01月-27日)</t>
+(25年-01月-28日)</t>
         </is>
       </c>
     </row>
@@ -44517,7 +44509,7 @@
           <t>A | 1002呎 (3房)
 $3395万
 $33,882/呎
-(25年-07月-02日)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -44525,7 +44517,7 @@
           <t>B | 1076呎 (4+房)
 $4188万
 $38,922/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
     </row>
@@ -44540,7 +44532,7 @@
           <t>A | 920呎 (3房)
 $3380万
 $36,739/呎
-(25年-06月-05日)</t>
+(25年-06月-06日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -44548,7 +44540,7 @@
           <t>B | 1076呎 (4+房)
 $4090万
 $38,011/呎
-(25年-05月-27日)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -44563,7 +44555,7 @@
           <t>A | 920呎 (3房)
 $3359万
 $36,511/呎
-(25年-04月-29日)</t>
+(25年-04月-30日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -44571,7 +44563,7 @@
           <t>B | 1173呎 (4+房)
 $4066万
 $34,663/呎
-(24年-12月-03日)</t>
+(24年-12月-04日)</t>
         </is>
       </c>
     </row>
@@ -44586,7 +44578,7 @@
           <t>A | 920呎 (3房)
 $3330万
 $36,196/呎
-(24年-12月-30日)</t>
+(24年-12月-31日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -44594,7 +44586,7 @@
           <t>B | 1076呎 (4+房)
 $4037万
 $37,519/呎
-(25年-06月-04日)</t>
+(25年-06月-05日)</t>
         </is>
       </c>
     </row>
@@ -44609,7 +44601,7 @@
           <t>A | 920呎 (3房)
 $3318万
 $36,065/呎
-(24年-12月-19日)</t>
+(24年-12月-20日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -44617,7 +44609,7 @@
           <t>B | 1173呎 (4+房)
 $4016万
 $34,237/呎
-(25年-05月-15日)</t>
+(25年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -44632,7 +44624,7 @@
           <t>A | 1002呎 (3房)
 $3290万
 $32,834/呎
-(25年-01月-15日)</t>
+(25年-01月-16日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -44640,7 +44632,7 @@
           <t>B | 1076呎 (3房)
 $4087万
 $37,983/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
     </row>
@@ -44655,7 +44647,7 @@
           <t>A | 920呎 (3房)
 $3271万
 $35,554/呎
-(25年-04月-29日)</t>
+(25年-04月-30日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -44663,7 +44655,7 @@
           <t>B | 1076呎 (4+房)
 $3958万
 $36,784/呎
-(25年-06月-03日)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
     </row>
@@ -44678,7 +44670,7 @@
           <t>A | 920呎 (3房)
 $3295万
 $35,815/呎
-(25年-09月-03日)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -44686,7 +44678,7 @@
           <t>B | 1076呎 (4+房)
 $3988万
 $37,063/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
     </row>
@@ -44701,7 +44693,7 @@
           <t>A | 920呎 (3房)
 $3416万
 $37,130/呎
-(25年-12月-16日)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -44709,7 +44701,7 @@
           <t>B | 1076呎 (4+房)
 $4058万
 $37,714/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -44847,7 +44839,7 @@
           <t>A | 1890呎 (4+房)
 $10395万
 $55,000/呎
-(23年-06月-07日)</t>
+(23年-06月-08日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -45043,7 +45035,7 @@
           <t>B | 1298呎 (4+房)
 $5013万
 $38,621/呎
-(24年-04月-04日)</t>
+(24年-04月-05日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -45074,7 +45066,7 @@
           <t>A | 1165呎 (4+房)
 $5381万
 $46,189/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -45108,7 +45100,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 1259呎 (4+房)
 招标单位
@@ -45121,7 +45113,7 @@
           <t>B | 1298呎 (4+房)
 $4936万
 $38,028/呎
-(24年-04月-24日)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -45152,10 +45144,10 @@
           <t>A | 1165呎 (4+房)
 $4898万
 $42,043/呎
-(25年-09月-21日)</t>
-        </is>
-      </c>
-      <c r="C13" s="24" t="inlineStr">
+(25年-09月-22日)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 1298呎 (4+房)
 招标单位
@@ -45186,7 +45178,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 1259呎 (4+房)
 招标单位
@@ -45194,7 +45186,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 1298呎 (4+房)
 招标单位
@@ -45230,7 +45222,7 @@
           <t>A | 1259呎 (4+房)
 $4712万
 $37,426/呎
-(24年-11月-07日)</t>
+(24年-11月-08日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -45238,7 +45230,7 @@
           <t>B | 1298呎 (4+房)
 $4808万
 $37,042/呎
-(24年-05月-02日)</t>
+(24年-05月-03日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -45269,7 +45261,7 @@
           <t>A | 1259呎 (4+房)
 $4663万
 $37,037/呎
-(24年-04月-28日)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -45277,7 +45269,7 @@
           <t>B | 1298呎 (4+房)
 $4771万
 $36,757/呎
-(24年-04月-29日)</t>
+(24年-04月-30日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -45308,7 +45300,7 @@
           <t>A | 1165呎 (4+房)
 $4988万
 $42,815/呎
-(26年-02月-03日)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -45316,7 +45308,7 @@
           <t>B | 1204呎 (4+房)
 $5103万
 $42,384/呎
-(26年-02月-03日)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -45355,7 +45347,7 @@
           <t>B | 1298呎 (4+房)
 $4765万
 $36,710/呎
-(24年-04月-04日)</t>
+(24年-04月-05日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -45381,7 +45373,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 1259呎 (4+房)
 招标单位
@@ -45394,7 +45386,7 @@
           <t>B | 1298呎 (4+房)
 $4688万
 $36,117/呎
-(24年-04月-18日)</t>
+(24年-04月-19日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -45425,7 +45417,7 @@
           <t>A | 1165呎 (4+房)
 $4800万
 $41,202/呎
-(26年-03月-22日)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -45433,7 +45425,7 @@
           <t>B | 1298呎 (4+房)
 $4657万
 $35,878/呎
-(23年-06月-06日)</t>
+(23年-06月-07日)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -45503,7 +45495,7 @@
           <t>A | 1165呎 (4+房)
 $4750万
 $40,773/呎
-(26年-02月-09日)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -45511,7 +45503,7 @@
           <t>B | 1204呎 (4+房)
 $5153万
 $42,799/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -45542,7 +45534,7 @@
           <t>A | 1165呎 (4+房)
 $4548万
 $39,039/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -45550,7 +45542,7 @@
           <t>B | 1298呎 (4+房)
 $4646万
 $35,794/呎
-(25年-07月-21日)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -45581,7 +45573,7 @@
           <t>A | 1165呎 (4+房)
 $4930万
 $42,318/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -45589,7 +45581,7 @@
           <t>B | 1204呎 (4+房)
 $4977万
 $41,337/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -45620,7 +45612,7 @@
           <t>A | 1165呎 (4+房)
 $4550万
 $39,056/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -45628,7 +45620,7 @@
           <t>B | 1204呎 (4+房)
 $4900万
 $40,698/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -45659,10 +45651,10 @@
           <t>A | 1165呎 (4+房)
 $4520万
 $38,798/呎
-(26年-01月-26日)</t>
-        </is>
-      </c>
-      <c r="C26" s="24" t="inlineStr">
+(26年-01月-27日)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 1298呎 (4+房)
 招标单位
@@ -45693,7 +45685,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B27" s="24" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>A | 1259呎 (4+房)
 招标单位
@@ -45701,7 +45693,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>B | 1298呎 (4+房)
 招标单位
@@ -45732,7 +45724,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B28" s="24" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 1259呎 (4+房)
 招标单位
@@ -45893,7 +45885,7 @@
           <t>A | 908呎 (3房)
 $3904万
 $43,000/呎
-(23年-06月-27日)</t>
+(23年-06月-28日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -45910,7 +45902,7 @@
           <t>A | 900呎 (3房)
 $3199万
 $35,544/呎
-(23年-07月-31日)</t>
+(23年-08月-01日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -45918,7 +45910,7 @@
           <t>B | 836呎 (3房)
 $2949万
 $35,280/呎
-(24年-03月-20日)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -45926,7 +45918,7 @@
           <t>C | 907呎 (3房)
 $3127万
 $34,472/呎
-(24年-04月-02日)</t>
+(24年-04月-03日)</t>
         </is>
       </c>
     </row>
@@ -45941,7 +45933,7 @@
           <t>A | 900呎 (3房)
 $3397万
 $37,750/呎
-(23年-07月-17日)</t>
+(23年-07月-18日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -45949,7 +45941,7 @@
           <t>B | 836呎 (3房)
 $2680万
 $32,060/呎
-(23年-07月-17日)</t>
+(23年-07月-18日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -45957,7 +45949,7 @@
           <t>C | 907呎 (3房)
 $2916万
 $32,151/呎
-(23年-07月-17日)</t>
+(23年-07月-18日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-天泷.xlsx
+++ b/files/九龙-启德-天泷.xlsx
@@ -12083,23 +12083,19 @@
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H171" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I171" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H171" s="5" t="n">
+        <v>41632000</v>
+      </c>
+      <c r="I171" s="5" t="n">
+        <v>37779</v>
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
@@ -12108,12 +12104,12 @@
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L171" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M171" s="3" t="inlineStr">
@@ -12123,7 +12119,7 @@
       </c>
       <c r="N171" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -34725,7 +34721,7 @@
       </c>
       <c r="F504" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G504" s="3" t="inlineStr">
@@ -34735,12 +34731,12 @@
       </c>
       <c r="H504" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I504" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J504" s="3" t="inlineStr">
@@ -34750,12 +34746,12 @@
       </c>
       <c r="K504" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L504" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M504" s="3" t="inlineStr">
@@ -34765,7 +34761,7 @@
       </c>
       <c r="N504" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -40943,7 +40939,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -40953,7 +40949,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -41266,12 +41262,12 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 1102呎 (3房)
-招标单位
--
-(在售)</t>
+$4163万
+$37,779/呎
+(26年-07月-31日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -44777,7 +44773,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -44797,7 +44793,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>63</t>
         </is>
       </c>
     </row>
@@ -45186,12 +45182,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 1298呎 (4+房)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">

--- a/files/九龙-启德-天泷.xlsx
+++ b/files/九龙-启德-天泷.xlsx
@@ -7557,23 +7557,19 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I104" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>45520000</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>38806</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
@@ -7582,12 +7578,12 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M104" s="3" t="inlineStr">
@@ -7597,7 +7593,7 @@
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12075,7 @@
         </is>
       </c>
       <c r="E171" s="4" t="n">
-        <v>1102</v>
+        <v>1027</v>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
@@ -12095,7 +12091,7 @@
         <v>41632000</v>
       </c>
       <c r="I171" s="5" t="n">
-        <v>37779</v>
+        <v>40537</v>
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
@@ -34721,23 +34717,19 @@
       </c>
       <c r="F504" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H504" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I504" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H504" s="5" t="n">
+        <v>55300000</v>
+      </c>
+      <c r="I504" s="5" t="n">
+        <v>42604</v>
       </c>
       <c r="J504" s="3" t="inlineStr">
         <is>
@@ -34791,23 +34783,19 @@
       </c>
       <c r="F505" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H505" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I505" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="H505" s="5" t="n">
+        <v>54750000</v>
+      </c>
+      <c r="I505" s="5" t="n">
+        <v>43487</v>
       </c>
       <c r="J505" s="3" t="inlineStr">
         <is>
@@ -34816,12 +34804,12 @@
       </c>
       <c r="K505" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L505" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M505" s="3" t="inlineStr">
@@ -34831,7 +34819,7 @@
       </c>
       <c r="N505" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -40182,7 +40170,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -40192,7 +40180,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -40436,12 +40424,12 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 1173呎 (4+房)
-招标单位
--
-(在售)</t>
+$4552万
+$38,806/呎
+(26年-08月-03日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -41264,9 +41252,9 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>A | 1102呎 (3房)
+          <t>A | 1027呎 (3房)
 $4163万
-$37,779/呎
+$40,537/呎
 (26年-07月-31日)</t>
         </is>
       </c>
@@ -44773,7 +44761,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -44783,7 +44771,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -44793,7 +44781,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>62</t>
         </is>
       </c>
     </row>
@@ -45174,20 +45162,20 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 1259呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
+$5475万
+$43,487/呎
+(26年-08月-04日)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 1298呎 (4+房)
--
--
-(待售)</t>
+$5530万
+$42,604/呎
+(26年-08月-07日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">

--- a/files/九龙-启德-天泷.xlsx
+++ b/files/九龙-启德-天泷.xlsx
@@ -12347,7 +12347,7 @@
         </is>
       </c>
       <c r="E175" s="4" t="n">
-        <v>1102</v>
+        <v>1027</v>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>37740000</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>34247</v>
+        <v>36748</v>
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
@@ -41291,9 +41291,9 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>A | 1102呎 (3房)
+          <t>A | 1027呎 (3房)
 $3774万
-$34,247/呎
+$36,748/呎
 (24年-11月-22日)</t>
         </is>
       </c>

--- a/files/九龙-启德-天泷.xlsx
+++ b/files/九龙-启德-天泷.xlsx
@@ -128,13 +128,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
@@ -285,10 +285,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -783,23 +783,19 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>16383000</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>25800</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -808,12 +804,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -823,7 +819,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -39200,7 +39196,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -39210,7 +39206,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -39261,12 +39257,12 @@
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
-      <c r="D5" s="22" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 635呎 (3房)
-招标单位
--
-(在售)</t>
+$1638万
+$25,800/呎
+(26年-08月-13日)</t>
         </is>
       </c>
     </row>
@@ -39276,7 +39272,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 1428呎 (4+房)
 -
@@ -39284,7 +39280,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 1258呎 (4+房)
 -
@@ -39307,7 +39303,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 1428呎 (4+房)
 -
@@ -39315,7 +39311,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1258呎 (4+房)
 -
@@ -39338,7 +39334,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 1428呎 (4+房)
 -
@@ -39346,7 +39342,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 1258呎 (4+房)
 -
@@ -39369,7 +39365,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>A | 1428呎 (4+房)
 招标单位
@@ -39377,7 +39373,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>B | 1258呎 (4+房)
 招标单位
@@ -39408,7 +39404,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 1258呎 (4+房)
 -
@@ -39439,7 +39435,7 @@
 (26年-06月-17日)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>B | 1258呎 (4+房)
 招标单位
@@ -39687,7 +39683,7 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>B | 1258呎 (4+房)
 招标单位
@@ -39772,7 +39768,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 1428呎 (4+房)
 -
@@ -39780,7 +39776,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 1258呎 (4+房)
 -
@@ -40217,7 +40213,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>A | 1181呎 (4+房)
 -
@@ -40225,7 +40221,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>B | 1006呎 (3房)
 -
@@ -40240,7 +40236,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 1173呎 (4+房)
 -
@@ -40248,7 +40244,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>B | 1002呎 (3房)
 招标单位
@@ -40263,7 +40259,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 1173呎 (4+房)
 -
@@ -40271,7 +40267,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>B | 920呎 (3房)
 招标单位
@@ -40286,7 +40282,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>A | 1173呎 (4+房)
 招标单位
@@ -40309,7 +40305,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>A | 1173呎 (4+房)
 招标单位
@@ -40332,7 +40328,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 1173呎 (4+房)
 -
@@ -40355,7 +40351,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>A | 1173呎 (4+房)
 招标单位
@@ -40378,7 +40374,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 1173呎 (4+房)
 招标单位
@@ -40993,7 +40989,7 @@
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41001,7 +40997,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41016,7 +41012,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 1102呎 (3房)
 -
@@ -41024,7 +41020,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 1085呎 (3房)
 -
@@ -41032,7 +41028,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41040,7 +41036,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41055,7 +41051,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 1102呎 (3房)
 -
@@ -41063,7 +41059,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1085呎 (3房)
 -
@@ -41071,7 +41067,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41079,7 +41075,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41094,7 +41090,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 1102呎 (3房)
 -
@@ -41102,7 +41098,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 1085呎 (3房)
 -
@@ -41110,7 +41106,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41118,7 +41114,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41133,7 +41129,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>A | 1102呎 (3房)
 招标单位
@@ -41141,7 +41137,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>B | 1085呎 (3房)
 招标单位
@@ -41149,7 +41145,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41157,7 +41153,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41188,7 +41184,7 @@
 (24年-11月-22日)</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41196,7 +41192,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41211,7 +41207,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>A | 1102呎 (3房)
 招标单位
@@ -41227,7 +41223,7 @@
 (25年-12月-17日)</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41235,7 +41231,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41266,7 +41262,7 @@
 (25年-01月-15日)</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41274,7 +41270,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41305,7 +41301,7 @@
 (24年-12月-03日)</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41313,7 +41309,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41344,7 +41340,7 @@
 (25年-01月-10日)</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41352,7 +41348,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41383,7 +41379,7 @@
 (24年-04月-29日)</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41391,7 +41387,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41422,7 +41418,7 @@
 (24年-12月-03日)</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41430,7 +41426,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41461,7 +41457,7 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41469,7 +41465,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41500,7 +41496,7 @@
 (24年-12月-06日)</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41508,7 +41504,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41539,7 +41535,7 @@
 (24年-11月-22日)</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41547,7 +41543,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41578,7 +41574,7 @@
 (24年-12月-06日)</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41586,7 +41582,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41617,7 +41613,7 @@
 (24年-11月-22日)</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41625,7 +41621,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41656,7 +41652,7 @@
 (24年-11月-22日)</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41664,7 +41660,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41695,7 +41691,7 @@
 (24年-11月-22日)</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41703,7 +41699,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41734,7 +41730,7 @@
 (24年-11月-18日)</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41742,7 +41738,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41773,7 +41769,7 @@
 (24年-12月-04日)</t>
         </is>
       </c>
-      <c r="D25" s="23" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41781,7 +41777,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41812,7 +41808,7 @@
 (24年-11月-18日)</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41820,7 +41816,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41851,7 +41847,7 @@
 (24年-11月-19日)</t>
         </is>
       </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41859,7 +41855,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41890,7 +41886,7 @@
 (24年-12月-16日)</t>
         </is>
       </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41898,7 +41894,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41929,7 +41925,7 @@
 (24年-11月-22日)</t>
         </is>
       </c>
-      <c r="D29" s="23" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41937,7 +41933,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -41968,7 +41964,7 @@
 (24年-12月-06日)</t>
         </is>
       </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -41976,7 +41972,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E30" s="23" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -42007,7 +42003,7 @@
 (25年-02月-28日)</t>
         </is>
       </c>
-      <c r="D31" s="23" t="inlineStr">
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -42015,7 +42011,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -42046,7 +42042,7 @@
 (26年-04月-23日)</t>
         </is>
       </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="D32" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -42054,7 +42050,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E32" s="23" t="inlineStr">
+      <c r="E32" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -42180,7 +42176,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>A | 1383呎 (4+房)
 -
@@ -42188,7 +42184,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>B | 1384呎 (3房)
 -
@@ -42203,7 +42199,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 1382呎 (4+房)
 -
@@ -42211,7 +42207,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 1382呎 (4+房)
 -
@@ -42226,7 +42222,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 1382呎 (4+房)
 -
@@ -42234,7 +42230,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1382呎 (4+房)
 -
@@ -42249,7 +42245,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>A | 1382呎 (4+房)
 招标单位
@@ -42257,7 +42253,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>B | 1382呎 (4+房)
 招标单位
@@ -42272,7 +42268,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>A | 1382呎 (4+房)
 招标单位
@@ -42295,7 +42291,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>A | 1382呎 (4+房)
 招标单位
@@ -42956,7 +42952,7 @@
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -42964,7 +42960,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -42979,7 +42975,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 1085呎 (2房)
 -
@@ -42987,7 +42983,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 1102呎 (3房)
 -
@@ -42995,7 +42991,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43003,7 +42999,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43018,7 +43014,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 1085呎 (3房)
 -
@@ -43026,7 +43022,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1102呎 (3房)
 -
@@ -43034,7 +43030,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43042,7 +43038,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43057,7 +43053,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 1085呎 (3房)
 -
@@ -43065,7 +43061,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 1102呎 (3房)
 -
@@ -43073,7 +43069,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43081,7 +43077,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43096,7 +43092,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>A | 1085呎 (3房)
 招标单位
@@ -43104,7 +43100,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>B | 1102呎 (3房)
 招标单位
@@ -43112,7 +43108,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43120,7 +43116,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43135,7 +43131,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>A | 1085呎 (3房)
 招标单位
@@ -43143,7 +43139,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 1102呎 (3房)
 招标单位
@@ -43151,7 +43147,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43159,7 +43155,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43190,7 +43186,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43198,7 +43194,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43221,7 +43217,7 @@
 (26年-04月-17日)</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 1102呎 (3房)
 -
@@ -43229,7 +43225,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43237,7 +43233,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43268,7 +43264,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43276,7 +43272,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43299,7 +43295,7 @@
 (26年-02月-25日)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 1102呎 (3房)
 招标单位
@@ -43307,7 +43303,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43315,7 +43311,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43346,7 +43342,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43354,7 +43350,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43385,7 +43381,7 @@
 (25年-10月-24日)</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43393,7 +43389,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43424,7 +43420,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43432,7 +43428,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43463,7 +43459,7 @@
 (25年-12月-10日)</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43471,7 +43467,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43502,7 +43498,7 @@
 (25年-12月-04日)</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43510,7 +43506,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43533,7 +43529,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 1102呎 (3房)
 -
@@ -43541,7 +43537,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43549,7 +43545,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43580,7 +43576,7 @@
 (25年-09月-10日)</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43588,7 +43584,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43619,7 +43615,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43627,7 +43623,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43658,7 +43654,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43666,7 +43662,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43697,7 +43693,7 @@
 (25年-05月-06日)</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43705,7 +43701,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43736,7 +43732,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="D25" s="23" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43744,7 +43740,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43775,7 +43771,7 @@
 (25年-05月-21日)</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43783,7 +43779,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43814,7 +43810,7 @@
 (25年-08月-20日)</t>
         </is>
       </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43822,7 +43818,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43853,7 +43849,7 @@
 (25年-09月-02日)</t>
         </is>
       </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43861,7 +43857,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43892,7 +43888,7 @@
 (26年-04月-30日)</t>
         </is>
       </c>
-      <c r="D29" s="23" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43900,7 +43896,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43931,7 +43927,7 @@
 (25年-04月-17日)</t>
         </is>
       </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43939,7 +43935,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E30" s="23" t="inlineStr">
+      <c r="E30" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -43962,7 +43958,7 @@
 (25年-04月-08日)</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>B | 1117呎 (3房)
 招标单位
@@ -43970,7 +43966,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D31" s="23" t="inlineStr">
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -43978,7 +43974,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -44001,7 +43997,7 @@
 (25年-05月-14日)</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>B | 1117呎 (3房)
 招标单位
@@ -44009,7 +44005,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="D32" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -44017,7 +44013,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E32" s="23" t="inlineStr">
+      <c r="E32" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -44143,7 +44139,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>A | 1006呎 (3房)
 -
@@ -44151,7 +44147,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>B | 1182呎 (4+房)
 -
@@ -44166,7 +44162,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 1002呎 (3房)
 -
@@ -44174,7 +44170,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 1173呎 (4+房)
 -
@@ -44189,7 +44185,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 1002呎 (3房)
 -
@@ -44197,7 +44193,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1173呎 (4+房)
 -
@@ -44212,7 +44208,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>A | 1002呎 (3房)
 招标单位
@@ -44220,7 +44216,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>B | 1173呎 (4+房)
 招标单位
@@ -44243,7 +44239,7 @@
 (26年-06月-01日)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>B | 1173呎 (4+房)
 招标单位
@@ -44827,7 +44823,7 @@
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -44835,7 +44831,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -44850,7 +44846,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 1259呎 (2房)
 -
@@ -44858,7 +44854,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 1298呎 (4+房)
 -
@@ -44866,7 +44862,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -44874,7 +44870,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -44889,7 +44885,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 1259呎 (4+房)
 -
@@ -44897,7 +44893,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1298呎 (4+房)
 -
@@ -44905,7 +44901,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -44913,7 +44909,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -44928,7 +44924,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 1259呎 (4+房)
 -
@@ -44936,7 +44932,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 1298呎 (4+房)
 -
@@ -44944,7 +44940,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -44952,7 +44948,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -44967,7 +44963,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 1259呎 (4+房)
 -
@@ -44975,7 +44971,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 1298呎 (4+房)
 -
@@ -44983,7 +44979,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -44991,7 +44987,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -45006,7 +45002,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 1259呎 (4+房)
 -
@@ -45022,7 +45018,7 @@
 (24年-04月-05日)</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -45030,7 +45026,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -45053,7 +45049,7 @@
 (26年-04月-24日)</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 1298呎 (4+房)
 -
@@ -45061,7 +45057,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -45069,7 +45065,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -45084,7 +45080,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 1259呎 (4+房)
 招标单位
@@ -45100,7 +45096,7 @@
 (24年-04月-25日)</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -45108,7 +45104,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -45131,7 +45127,7 @@
 (25年-09月-22日)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 1298呎 (4+房)
 招标单位
@@ -45139,7 +45135,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -45147,7 +45143,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -45178,7 +45174,7 @@
 (26年-08月-07日)</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -45186,7 +45182,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -45217,7 +45213,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -45225,7 +45221,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -45256,7 +45252,7 @@
 (24年-04月-30日)</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -45264,7 +45260,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -45295,7 +45291,7 @@
 (26年-02月-04日)</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -45303,7 +45299,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -45318,7 +45314,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 1259呎 (4+房)
 -
@@ -45334,7 +45330,7 @@
 (24年-04月-05日)</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -45342,7 +45338,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -45357,7 +45353,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>A | 1259呎 (4+房)
 招标单位
@@ -45373,7 +45369,7 @@
 (24年-04月-19日)</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -45381,7 +45377,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -45412,7 +45408,7 @@
 (23年-06月-07日)</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -45420,7 +45416,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -45435,7 +45431,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 1259呎 (4+房)
 -
@@ -45443,7 +45439,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 1298呎 (4+房)
 -
@@ -45451,7 +45447,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -45459,7 +45455,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -45490,7 +45486,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -45498,7 +45494,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -45529,7 +45525,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -45537,7 +45533,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -45568,7 +45564,7 @@
 (26年-06月-02日)</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -45576,7 +45572,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -45607,7 +45603,7 @@
 (26年-07月-09日)</t>
         </is>
       </c>
-      <c r="D25" s="23" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -45615,7 +45611,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -45638,7 +45634,7 @@
 (26年-01月-27日)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>B | 1298呎 (4+房)
 招标单位
@@ -45646,7 +45642,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -45654,7 +45650,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -45669,7 +45665,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>A | 1259呎 (4+房)
 招标单位
@@ -45677,7 +45673,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>B | 1298呎 (4+房)
 招标单位
@@ -45685,7 +45681,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -45693,7 +45689,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -
@@ -45708,7 +45704,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>A | 1259呎 (4+房)
 招标单位
@@ -45716,7 +45712,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>B | 1298呎 (4+房)
 -
@@ -45724,7 +45720,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 351呎 (1房)
 -
@@ -45732,7 +45728,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 351呎 (1房)
 -

--- a/files/九龙-启德-天泷.xlsx
+++ b/files/九龙-启德-天泷.xlsx
@@ -7549,7 +7549,7 @@
         </is>
       </c>
       <c r="E104" s="4" t="n">
-        <v>1173</v>
+        <v>1076</v>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
@@ -7558,14 +7558,14 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
         <v>45520000</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>38806</v>
+        <v>42305</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
@@ -40422,10 +40422,10 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>A | 1173呎 (4+房)
+          <t>A | 1076呎 (4+房)
 $4552万
-$38,806/呎
-(26年-08月-03日)</t>
+$42,305/呎
+(26年-08月-14日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">

--- a/files/九龙-启德-天泷.xlsx
+++ b/files/九龙-启德-天泷.xlsx
@@ -4412,7 +4412,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -12080,7 +12080,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -34775,7 +34775,7 @@
         </is>
       </c>
       <c r="E505" s="4" t="n">
-        <v>1259</v>
+        <v>1165</v>
       </c>
       <c r="F505" s="3" t="inlineStr">
         <is>
@@ -34784,14 +34784,14 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H505" s="5" t="n">
         <v>54750000</v>
       </c>
       <c r="I505" s="5" t="n">
-        <v>43487</v>
+        <v>46996</v>
       </c>
       <c r="J505" s="3" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
           <t>B | 1171呎 (4+房)
 $4790万
 $40,905/呎
-(26年-07月-20日)</t>
+(26年-08月-20日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -41251,7 +41251,7 @@
           <t>A | 1027呎 (3房)
 $4163万
 $40,537/呎
-(26年-07月-31日)</t>
+(26年-08月-21日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -45160,10 +45160,10 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>A | 1259呎 (4+房)
+          <t>A | 1165呎 (4+房)
 $5475万
-$43,487/呎
-(26年-08月-04日)</t>
+$46,996/呎
+(26年-08月-18日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
